--- a/experiment/DHTCUN_x4_nfs90_win24dvk5+2/results_HUTCN_DHTCUN_x4_nfs90_win24dvk5+2.xlsx
+++ b/experiment/DHTCUN_x4_nfs90_win24dvk5+2/results_HUTCN_DHTCUN_x4_nfs90_win24dvk5+2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Training Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Training Results" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E293"/>
+  <dimension ref="A1:E451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5429,8 +5429,2694 @@
       <c r="D293" t="n">
         <v>0.02403</v>
       </c>
-      <c r="E293" s="3" t="n">
+      <c r="E293" s="2" t="n">
         <v>32.71</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>293</v>
+      </c>
+      <c r="B294" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C294" t="n">
+        <v>0.02381</v>
+      </c>
+      <c r="D294" t="n">
+        <v>0.02381</v>
+      </c>
+      <c r="E294" t="n">
+        <v>32.744</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>294</v>
+      </c>
+      <c r="B295" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C295" t="n">
+        <v>0.02396</v>
+      </c>
+      <c r="D295" t="n">
+        <v>0.02396</v>
+      </c>
+      <c r="E295" t="n">
+        <v>32.735</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>295</v>
+      </c>
+      <c r="B296" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C296" t="n">
+        <v>0.02358</v>
+      </c>
+      <c r="D296" t="n">
+        <v>0.02358</v>
+      </c>
+      <c r="E296" s="2" t="n">
+        <v>32.745</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>296</v>
+      </c>
+      <c r="B297" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C297" t="n">
+        <v>0.02397</v>
+      </c>
+      <c r="D297" t="n">
+        <v>0.02397</v>
+      </c>
+      <c r="E297" s="2" t="n">
+        <v>32.755</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>297</v>
+      </c>
+      <c r="B298" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C298" t="n">
+        <v>0.02365</v>
+      </c>
+      <c r="D298" t="n">
+        <v>0.02365</v>
+      </c>
+      <c r="E298" s="2" t="n">
+        <v>32.767</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>298</v>
+      </c>
+      <c r="B299" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C299" t="n">
+        <v>0.02378</v>
+      </c>
+      <c r="D299" t="n">
+        <v>0.02378</v>
+      </c>
+      <c r="E299" t="n">
+        <v>32.738</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>299</v>
+      </c>
+      <c r="B300" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C300" t="n">
+        <v>0.02406</v>
+      </c>
+      <c r="D300" t="n">
+        <v>0.02406</v>
+      </c>
+      <c r="E300" t="n">
+        <v>32.758</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>300</v>
+      </c>
+      <c r="B301" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C301" t="n">
+        <v>0.02411</v>
+      </c>
+      <c r="D301" t="n">
+        <v>0.02411</v>
+      </c>
+      <c r="E301" t="n">
+        <v>32.756</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>301</v>
+      </c>
+      <c r="B302" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C302" t="n">
+        <v>0.02378</v>
+      </c>
+      <c r="D302" t="n">
+        <v>0.02378</v>
+      </c>
+      <c r="E302" t="n">
+        <v>32.758</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>302</v>
+      </c>
+      <c r="B303" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C303" t="n">
+        <v>0.02375</v>
+      </c>
+      <c r="D303" t="n">
+        <v>0.02375</v>
+      </c>
+      <c r="E303" t="n">
+        <v>32.752</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>303</v>
+      </c>
+      <c r="B304" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C304" t="n">
+        <v>0.02404</v>
+      </c>
+      <c r="D304" t="n">
+        <v>0.02404</v>
+      </c>
+      <c r="E304" t="n">
+        <v>32.765</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>304</v>
+      </c>
+      <c r="B305" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C305" t="n">
+        <v>0.02404</v>
+      </c>
+      <c r="D305" t="n">
+        <v>0.02404</v>
+      </c>
+      <c r="E305" t="n">
+        <v>32.749</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>305</v>
+      </c>
+      <c r="B306" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C306" t="n">
+        <v>0.02435</v>
+      </c>
+      <c r="D306" t="n">
+        <v>0.02435</v>
+      </c>
+      <c r="E306" t="n">
+        <v>32.754</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>306</v>
+      </c>
+      <c r="B307" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C307" t="n">
+        <v>0.0236</v>
+      </c>
+      <c r="D307" t="n">
+        <v>0.0236</v>
+      </c>
+      <c r="E307" t="n">
+        <v>32.756</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>307</v>
+      </c>
+      <c r="B308" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C308" t="n">
+        <v>0.02395</v>
+      </c>
+      <c r="D308" t="n">
+        <v>0.02395</v>
+      </c>
+      <c r="E308" t="n">
+        <v>32.756</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>308</v>
+      </c>
+      <c r="B309" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C309" t="n">
+        <v>0.02351</v>
+      </c>
+      <c r="D309" t="n">
+        <v>0.02351</v>
+      </c>
+      <c r="E309" t="n">
+        <v>32.759</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>309</v>
+      </c>
+      <c r="B310" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C310" t="n">
+        <v>0.0237</v>
+      </c>
+      <c r="D310" t="n">
+        <v>0.0237</v>
+      </c>
+      <c r="E310" t="n">
+        <v>32.76</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>310</v>
+      </c>
+      <c r="B311" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C311" t="n">
+        <v>0.02361</v>
+      </c>
+      <c r="D311" t="n">
+        <v>0.02361</v>
+      </c>
+      <c r="E311" t="n">
+        <v>32.758</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>311</v>
+      </c>
+      <c r="B312" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C312" t="n">
+        <v>0.02379</v>
+      </c>
+      <c r="D312" t="n">
+        <v>0.02379</v>
+      </c>
+      <c r="E312" s="2" t="n">
+        <v>32.772</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>312</v>
+      </c>
+      <c r="B313" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C313" t="n">
+        <v>0.02377</v>
+      </c>
+      <c r="D313" t="n">
+        <v>0.02377</v>
+      </c>
+      <c r="E313" s="2" t="n">
+        <v>32.772</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>313</v>
+      </c>
+      <c r="B314" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C314" t="n">
+        <v>0.02355</v>
+      </c>
+      <c r="D314" t="n">
+        <v>0.02355</v>
+      </c>
+      <c r="E314" t="n">
+        <v>32.763</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>314</v>
+      </c>
+      <c r="B315" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C315" t="n">
+        <v>0.02352</v>
+      </c>
+      <c r="D315" t="n">
+        <v>0.02352</v>
+      </c>
+      <c r="E315" t="n">
+        <v>32.755</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>315</v>
+      </c>
+      <c r="B316" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C316" t="n">
+        <v>0.02397</v>
+      </c>
+      <c r="D316" t="n">
+        <v>0.02397</v>
+      </c>
+      <c r="E316" s="2" t="n">
+        <v>32.777</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>316</v>
+      </c>
+      <c r="B317" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C317" t="n">
+        <v>0.02414</v>
+      </c>
+      <c r="D317" t="n">
+        <v>0.02414</v>
+      </c>
+      <c r="E317" t="n">
+        <v>32.767</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>317</v>
+      </c>
+      <c r="B318" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C318" t="n">
+        <v>0.02364</v>
+      </c>
+      <c r="D318" t="n">
+        <v>0.02364</v>
+      </c>
+      <c r="E318" t="n">
+        <v>32.761</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>318</v>
+      </c>
+      <c r="B319" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C319" t="n">
+        <v>0.0235</v>
+      </c>
+      <c r="D319" t="n">
+        <v>0.0235</v>
+      </c>
+      <c r="E319" t="n">
+        <v>32.753</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>319</v>
+      </c>
+      <c r="B320" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C320" t="n">
+        <v>0.02415</v>
+      </c>
+      <c r="D320" t="n">
+        <v>0.02415</v>
+      </c>
+      <c r="E320" t="n">
+        <v>32.772</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>320</v>
+      </c>
+      <c r="B321" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C321" t="n">
+        <v>0.02396</v>
+      </c>
+      <c r="D321" t="n">
+        <v>0.02396</v>
+      </c>
+      <c r="E321" s="2" t="n">
+        <v>32.778</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>321</v>
+      </c>
+      <c r="B322" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C322" t="n">
+        <v>0.0236</v>
+      </c>
+      <c r="D322" t="n">
+        <v>0.0236</v>
+      </c>
+      <c r="E322" t="n">
+        <v>32.771</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>322</v>
+      </c>
+      <c r="B323" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C323" t="n">
+        <v>0.02366</v>
+      </c>
+      <c r="D323" t="n">
+        <v>0.02366</v>
+      </c>
+      <c r="E323" t="n">
+        <v>32.771</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>323</v>
+      </c>
+      <c r="B324" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C324" t="n">
+        <v>0.02395</v>
+      </c>
+      <c r="D324" t="n">
+        <v>0.02395</v>
+      </c>
+      <c r="E324" t="n">
+        <v>32.769</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>324</v>
+      </c>
+      <c r="B325" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C325" t="n">
+        <v>0.02324</v>
+      </c>
+      <c r="D325" t="n">
+        <v>0.02324</v>
+      </c>
+      <c r="E325" t="n">
+        <v>32.751</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>325</v>
+      </c>
+      <c r="B326" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C326" t="n">
+        <v>0.02401</v>
+      </c>
+      <c r="D326" t="n">
+        <v>0.02401</v>
+      </c>
+      <c r="E326" t="n">
+        <v>32.72</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>326</v>
+      </c>
+      <c r="B327" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C327" t="n">
+        <v>0.02341</v>
+      </c>
+      <c r="D327" t="n">
+        <v>0.02341</v>
+      </c>
+      <c r="E327" s="2" t="n">
+        <v>32.783</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>327</v>
+      </c>
+      <c r="B328" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C328" t="n">
+        <v>0.02376</v>
+      </c>
+      <c r="D328" t="n">
+        <v>0.02376</v>
+      </c>
+      <c r="E328" t="n">
+        <v>32.781</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>328</v>
+      </c>
+      <c r="B329" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C329" t="n">
+        <v>0.02308</v>
+      </c>
+      <c r="D329" t="n">
+        <v>0.02308</v>
+      </c>
+      <c r="E329" t="n">
+        <v>32.76</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>329</v>
+      </c>
+      <c r="B330" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C330" t="n">
+        <v>0.02385</v>
+      </c>
+      <c r="D330" t="n">
+        <v>0.02385</v>
+      </c>
+      <c r="E330" t="n">
+        <v>32.774</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>330</v>
+      </c>
+      <c r="B331" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C331" t="n">
+        <v>0.02332</v>
+      </c>
+      <c r="D331" t="n">
+        <v>0.02332</v>
+      </c>
+      <c r="E331" t="n">
+        <v>32.767</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>331</v>
+      </c>
+      <c r="B332" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C332" t="n">
+        <v>0.0236</v>
+      </c>
+      <c r="D332" t="n">
+        <v>0.0236</v>
+      </c>
+      <c r="E332" t="n">
+        <v>32.755</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>332</v>
+      </c>
+      <c r="B333" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C333" t="n">
+        <v>0.02318</v>
+      </c>
+      <c r="D333" t="n">
+        <v>0.02318</v>
+      </c>
+      <c r="E333" t="n">
+        <v>32.768</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>333</v>
+      </c>
+      <c r="B334" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C334" t="n">
+        <v>0.02366</v>
+      </c>
+      <c r="D334" t="n">
+        <v>0.02366</v>
+      </c>
+      <c r="E334" t="n">
+        <v>32.766</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>334</v>
+      </c>
+      <c r="B335" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C335" t="n">
+        <v>0.02372</v>
+      </c>
+      <c r="D335" t="n">
+        <v>0.02372</v>
+      </c>
+      <c r="E335" t="n">
+        <v>32.76</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>335</v>
+      </c>
+      <c r="B336" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C336" t="n">
+        <v>0.02412</v>
+      </c>
+      <c r="D336" t="n">
+        <v>0.02412</v>
+      </c>
+      <c r="E336" t="n">
+        <v>32.763</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>336</v>
+      </c>
+      <c r="B337" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C337" t="n">
+        <v>0.02378</v>
+      </c>
+      <c r="D337" t="n">
+        <v>0.02378</v>
+      </c>
+      <c r="E337" t="n">
+        <v>32.768</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>337</v>
+      </c>
+      <c r="B338" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C338" t="n">
+        <v>0.02349</v>
+      </c>
+      <c r="D338" t="n">
+        <v>0.02349</v>
+      </c>
+      <c r="E338" t="n">
+        <v>32.767</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>338</v>
+      </c>
+      <c r="B339" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C339" t="n">
+        <v>0.02418</v>
+      </c>
+      <c r="D339" t="n">
+        <v>0.02418</v>
+      </c>
+      <c r="E339" t="n">
+        <v>32.765</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>339</v>
+      </c>
+      <c r="B340" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C340" t="n">
+        <v>0.02354</v>
+      </c>
+      <c r="D340" t="n">
+        <v>0.02354</v>
+      </c>
+      <c r="E340" t="n">
+        <v>32.739</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>340</v>
+      </c>
+      <c r="B341" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C341" t="n">
+        <v>0.02408</v>
+      </c>
+      <c r="D341" t="n">
+        <v>0.02408</v>
+      </c>
+      <c r="E341" t="n">
+        <v>32.773</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>341</v>
+      </c>
+      <c r="B342" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C342" t="n">
+        <v>0.0239</v>
+      </c>
+      <c r="D342" t="n">
+        <v>0.0239</v>
+      </c>
+      <c r="E342" t="n">
+        <v>32.732</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>342</v>
+      </c>
+      <c r="B343" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C343" t="n">
+        <v>0.0238</v>
+      </c>
+      <c r="D343" t="n">
+        <v>0.0238</v>
+      </c>
+      <c r="E343" t="n">
+        <v>32.752</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>343</v>
+      </c>
+      <c r="B344" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C344" t="n">
+        <v>0.02401</v>
+      </c>
+      <c r="D344" t="n">
+        <v>0.02401</v>
+      </c>
+      <c r="E344" s="2" t="n">
+        <v>32.787</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>344</v>
+      </c>
+      <c r="B345" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C345" t="n">
+        <v>0.02321</v>
+      </c>
+      <c r="D345" t="n">
+        <v>0.02321</v>
+      </c>
+      <c r="E345" t="n">
+        <v>32.758</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>345</v>
+      </c>
+      <c r="B346" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C346" t="n">
+        <v>0.02355</v>
+      </c>
+      <c r="D346" t="n">
+        <v>0.02355</v>
+      </c>
+      <c r="E346" t="n">
+        <v>32.778</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>346</v>
+      </c>
+      <c r="B347" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C347" t="n">
+        <v>0.02368</v>
+      </c>
+      <c r="D347" t="n">
+        <v>0.02368</v>
+      </c>
+      <c r="E347" t="n">
+        <v>32.768</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>347</v>
+      </c>
+      <c r="B348" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C348" t="n">
+        <v>0.02386</v>
+      </c>
+      <c r="D348" t="n">
+        <v>0.02386</v>
+      </c>
+      <c r="E348" t="n">
+        <v>32.764</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>348</v>
+      </c>
+      <c r="B349" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C349" t="n">
+        <v>0.02378</v>
+      </c>
+      <c r="D349" t="n">
+        <v>0.02378</v>
+      </c>
+      <c r="E349" t="n">
+        <v>32.757</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>349</v>
+      </c>
+      <c r="B350" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C350" t="n">
+        <v>0.02384</v>
+      </c>
+      <c r="D350" t="n">
+        <v>0.02384</v>
+      </c>
+      <c r="E350" t="n">
+        <v>32.762</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>350</v>
+      </c>
+      <c r="B351" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="C351" t="n">
+        <v>0.02376</v>
+      </c>
+      <c r="D351" t="n">
+        <v>0.02376</v>
+      </c>
+      <c r="E351" t="n">
+        <v>32.782</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>351</v>
+      </c>
+      <c r="B352" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C352" t="n">
+        <v>0.02352</v>
+      </c>
+      <c r="D352" t="n">
+        <v>0.02352</v>
+      </c>
+      <c r="E352" t="n">
+        <v>32.78</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>352</v>
+      </c>
+      <c r="B353" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C353" t="n">
+        <v>0.02401</v>
+      </c>
+      <c r="D353" t="n">
+        <v>0.02401</v>
+      </c>
+      <c r="E353" s="2" t="n">
+        <v>32.793</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>353</v>
+      </c>
+      <c r="B354" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C354" t="n">
+        <v>0.02354</v>
+      </c>
+      <c r="D354" t="n">
+        <v>0.02354</v>
+      </c>
+      <c r="E354" t="n">
+        <v>32.785</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>354</v>
+      </c>
+      <c r="B355" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C355" t="n">
+        <v>0.02374</v>
+      </c>
+      <c r="D355" t="n">
+        <v>0.02374</v>
+      </c>
+      <c r="E355" t="n">
+        <v>32.769</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>355</v>
+      </c>
+      <c r="B356" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C356" t="n">
+        <v>0.02367</v>
+      </c>
+      <c r="D356" t="n">
+        <v>0.02367</v>
+      </c>
+      <c r="E356" t="n">
+        <v>32.774</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>356</v>
+      </c>
+      <c r="B357" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C357" t="n">
+        <v>0.02371</v>
+      </c>
+      <c r="D357" t="n">
+        <v>0.02371</v>
+      </c>
+      <c r="E357" t="n">
+        <v>32.772</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>357</v>
+      </c>
+      <c r="B358" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C358" t="n">
+        <v>0.02388</v>
+      </c>
+      <c r="D358" t="n">
+        <v>0.02388</v>
+      </c>
+      <c r="E358" t="n">
+        <v>32.776</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>358</v>
+      </c>
+      <c r="B359" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C359" t="n">
+        <v>0.0235</v>
+      </c>
+      <c r="D359" t="n">
+        <v>0.0235</v>
+      </c>
+      <c r="E359" t="n">
+        <v>32.769</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>359</v>
+      </c>
+      <c r="B360" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C360" t="n">
+        <v>0.02388</v>
+      </c>
+      <c r="D360" t="n">
+        <v>0.02388</v>
+      </c>
+      <c r="E360" t="n">
+        <v>32.787</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>360</v>
+      </c>
+      <c r="B361" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C361" t="n">
+        <v>0.02356</v>
+      </c>
+      <c r="D361" t="n">
+        <v>0.02356</v>
+      </c>
+      <c r="E361" t="n">
+        <v>32.79</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>361</v>
+      </c>
+      <c r="B362" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C362" t="n">
+        <v>0.02372</v>
+      </c>
+      <c r="D362" t="n">
+        <v>0.02372</v>
+      </c>
+      <c r="E362" t="n">
+        <v>32.766</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>362</v>
+      </c>
+      <c r="B363" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C363" t="n">
+        <v>0.02397</v>
+      </c>
+      <c r="D363" t="n">
+        <v>0.02397</v>
+      </c>
+      <c r="E363" t="n">
+        <v>32.778</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>363</v>
+      </c>
+      <c r="B364" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C364" t="n">
+        <v>0.02403</v>
+      </c>
+      <c r="D364" t="n">
+        <v>0.02403</v>
+      </c>
+      <c r="E364" t="n">
+        <v>32.783</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>364</v>
+      </c>
+      <c r="B365" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C365" t="n">
+        <v>0.02371</v>
+      </c>
+      <c r="D365" t="n">
+        <v>0.02371</v>
+      </c>
+      <c r="E365" t="n">
+        <v>32.789</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>365</v>
+      </c>
+      <c r="B366" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C366" t="n">
+        <v>0.02368</v>
+      </c>
+      <c r="D366" t="n">
+        <v>0.02368</v>
+      </c>
+      <c r="E366" t="n">
+        <v>32.777</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>366</v>
+      </c>
+      <c r="B367" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C367" t="n">
+        <v>0.02395</v>
+      </c>
+      <c r="D367" t="n">
+        <v>0.02395</v>
+      </c>
+      <c r="E367" t="n">
+        <v>32.785</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>367</v>
+      </c>
+      <c r="B368" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C368" t="n">
+        <v>0.02396</v>
+      </c>
+      <c r="D368" t="n">
+        <v>0.02396</v>
+      </c>
+      <c r="E368" t="n">
+        <v>32.775</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>368</v>
+      </c>
+      <c r="B369" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C369" t="n">
+        <v>0.02428</v>
+      </c>
+      <c r="D369" t="n">
+        <v>0.02428</v>
+      </c>
+      <c r="E369" t="n">
+        <v>32.782</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="n">
+        <v>369</v>
+      </c>
+      <c r="B370" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C370" t="n">
+        <v>0.02353</v>
+      </c>
+      <c r="D370" t="n">
+        <v>0.02353</v>
+      </c>
+      <c r="E370" t="n">
+        <v>32.785</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>370</v>
+      </c>
+      <c r="B371" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C371" t="n">
+        <v>0.02387</v>
+      </c>
+      <c r="D371" t="n">
+        <v>0.02387</v>
+      </c>
+      <c r="E371" t="n">
+        <v>32.789</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>371</v>
+      </c>
+      <c r="B372" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C372" t="n">
+        <v>0.02343</v>
+      </c>
+      <c r="D372" t="n">
+        <v>0.02343</v>
+      </c>
+      <c r="E372" t="n">
+        <v>32.78</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>372</v>
+      </c>
+      <c r="B373" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C373" t="n">
+        <v>0.02361</v>
+      </c>
+      <c r="D373" t="n">
+        <v>0.02361</v>
+      </c>
+      <c r="E373" t="n">
+        <v>32.785</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>373</v>
+      </c>
+      <c r="B374" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C374" t="n">
+        <v>0.02356</v>
+      </c>
+      <c r="D374" t="n">
+        <v>0.02356</v>
+      </c>
+      <c r="E374" t="n">
+        <v>32.786</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>374</v>
+      </c>
+      <c r="B375" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C375" t="n">
+        <v>0.02371</v>
+      </c>
+      <c r="D375" t="n">
+        <v>0.02371</v>
+      </c>
+      <c r="E375" t="n">
+        <v>32.792</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>375</v>
+      </c>
+      <c r="B376" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C376" t="n">
+        <v>0.0237</v>
+      </c>
+      <c r="D376" t="n">
+        <v>0.0237</v>
+      </c>
+      <c r="E376" t="n">
+        <v>32.789</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>376</v>
+      </c>
+      <c r="B377" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C377" t="n">
+        <v>0.0235</v>
+      </c>
+      <c r="D377" t="n">
+        <v>0.0235</v>
+      </c>
+      <c r="E377" t="n">
+        <v>32.779</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>377</v>
+      </c>
+      <c r="B378" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C378" t="n">
+        <v>0.02347</v>
+      </c>
+      <c r="D378" t="n">
+        <v>0.02347</v>
+      </c>
+      <c r="E378" t="n">
+        <v>32.78</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>378</v>
+      </c>
+      <c r="B379" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C379" t="n">
+        <v>0.02391</v>
+      </c>
+      <c r="D379" t="n">
+        <v>0.02391</v>
+      </c>
+      <c r="E379" s="2" t="n">
+        <v>32.794</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>379</v>
+      </c>
+      <c r="B380" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C380" t="n">
+        <v>0.0241</v>
+      </c>
+      <c r="D380" t="n">
+        <v>0.0241</v>
+      </c>
+      <c r="E380" t="n">
+        <v>32.789</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>380</v>
+      </c>
+      <c r="B381" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C381" t="n">
+        <v>0.02356</v>
+      </c>
+      <c r="D381" t="n">
+        <v>0.02356</v>
+      </c>
+      <c r="E381" t="n">
+        <v>32.781</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>381</v>
+      </c>
+      <c r="B382" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C382" t="n">
+        <v>0.02348</v>
+      </c>
+      <c r="D382" t="n">
+        <v>0.02348</v>
+      </c>
+      <c r="E382" t="n">
+        <v>32.777</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>382</v>
+      </c>
+      <c r="B383" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C383" t="n">
+        <v>0.02408</v>
+      </c>
+      <c r="D383" t="n">
+        <v>0.02408</v>
+      </c>
+      <c r="E383" t="n">
+        <v>32.794</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>383</v>
+      </c>
+      <c r="B384" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C384" t="n">
+        <v>0.02391</v>
+      </c>
+      <c r="D384" t="n">
+        <v>0.02391</v>
+      </c>
+      <c r="E384" t="n">
+        <v>32.794</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>384</v>
+      </c>
+      <c r="B385" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C385" t="n">
+        <v>0.02354</v>
+      </c>
+      <c r="D385" t="n">
+        <v>0.02354</v>
+      </c>
+      <c r="E385" t="n">
+        <v>32.793</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="n">
+        <v>385</v>
+      </c>
+      <c r="B386" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C386" t="n">
+        <v>0.02362</v>
+      </c>
+      <c r="D386" t="n">
+        <v>0.02362</v>
+      </c>
+      <c r="E386" t="n">
+        <v>32.787</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="n">
+        <v>386</v>
+      </c>
+      <c r="B387" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C387" t="n">
+        <v>0.02389</v>
+      </c>
+      <c r="D387" t="n">
+        <v>0.02389</v>
+      </c>
+      <c r="E387" t="n">
+        <v>32.789</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="n">
+        <v>387</v>
+      </c>
+      <c r="B388" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C388" t="n">
+        <v>0.02319</v>
+      </c>
+      <c r="D388" t="n">
+        <v>0.02319</v>
+      </c>
+      <c r="E388" t="n">
+        <v>32.774</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="n">
+        <v>388</v>
+      </c>
+      <c r="B389" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C389" t="n">
+        <v>0.02395</v>
+      </c>
+      <c r="D389" t="n">
+        <v>0.02395</v>
+      </c>
+      <c r="E389" t="n">
+        <v>32.758</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="n">
+        <v>389</v>
+      </c>
+      <c r="B390" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C390" t="n">
+        <v>0.02334</v>
+      </c>
+      <c r="D390" t="n">
+        <v>0.02334</v>
+      </c>
+      <c r="E390" s="2" t="n">
+        <v>32.803</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="n">
+        <v>390</v>
+      </c>
+      <c r="B391" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C391" t="n">
+        <v>0.02369</v>
+      </c>
+      <c r="D391" t="n">
+        <v>0.02369</v>
+      </c>
+      <c r="E391" t="n">
+        <v>32.788</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="n">
+        <v>391</v>
+      </c>
+      <c r="B392" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C392" t="n">
+        <v>0.02302</v>
+      </c>
+      <c r="D392" t="n">
+        <v>0.02302</v>
+      </c>
+      <c r="E392" t="n">
+        <v>32.777</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="n">
+        <v>392</v>
+      </c>
+      <c r="B393" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C393" t="n">
+        <v>0.02377</v>
+      </c>
+      <c r="D393" t="n">
+        <v>0.02377</v>
+      </c>
+      <c r="E393" t="n">
+        <v>32.788</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>393</v>
+      </c>
+      <c r="B394" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C394" t="n">
+        <v>0.02328</v>
+      </c>
+      <c r="D394" t="n">
+        <v>0.02328</v>
+      </c>
+      <c r="E394" t="n">
+        <v>32.789</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>394</v>
+      </c>
+      <c r="B395" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C395" t="n">
+        <v>0.02354</v>
+      </c>
+      <c r="D395" t="n">
+        <v>0.02354</v>
+      </c>
+      <c r="E395" t="n">
+        <v>32.768</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>395</v>
+      </c>
+      <c r="B396" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C396" t="n">
+        <v>0.02311</v>
+      </c>
+      <c r="D396" t="n">
+        <v>0.02311</v>
+      </c>
+      <c r="E396" t="n">
+        <v>32.78</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>396</v>
+      </c>
+      <c r="B397" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C397" t="n">
+        <v>0.02358</v>
+      </c>
+      <c r="D397" t="n">
+        <v>0.02358</v>
+      </c>
+      <c r="E397" t="n">
+        <v>32.779</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>397</v>
+      </c>
+      <c r="B398" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C398" t="n">
+        <v>0.02367</v>
+      </c>
+      <c r="D398" t="n">
+        <v>0.02367</v>
+      </c>
+      <c r="E398" t="n">
+        <v>32.782</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>398</v>
+      </c>
+      <c r="B399" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C399" t="n">
+        <v>0.02405</v>
+      </c>
+      <c r="D399" t="n">
+        <v>0.02405</v>
+      </c>
+      <c r="E399" t="n">
+        <v>32.78</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="n">
+        <v>399</v>
+      </c>
+      <c r="B400" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C400" t="n">
+        <v>0.02374</v>
+      </c>
+      <c r="D400" t="n">
+        <v>0.02374</v>
+      </c>
+      <c r="E400" t="n">
+        <v>32.789</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="n">
+        <v>400</v>
+      </c>
+      <c r="B401" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C401" t="n">
+        <v>0.02345</v>
+      </c>
+      <c r="D401" t="n">
+        <v>0.02345</v>
+      </c>
+      <c r="E401" t="n">
+        <v>32.781</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="n">
+        <v>401</v>
+      </c>
+      <c r="B402" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C402" t="n">
+        <v>0.02414</v>
+      </c>
+      <c r="D402" t="n">
+        <v>0.02414</v>
+      </c>
+      <c r="E402" t="n">
+        <v>32.779</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="n">
+        <v>402</v>
+      </c>
+      <c r="B403" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C403" t="n">
+        <v>0.0235</v>
+      </c>
+      <c r="D403" t="n">
+        <v>0.0235</v>
+      </c>
+      <c r="E403" t="n">
+        <v>32.769</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="n">
+        <v>403</v>
+      </c>
+      <c r="B404" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C404" t="n">
+        <v>0.02401</v>
+      </c>
+      <c r="D404" t="n">
+        <v>0.02401</v>
+      </c>
+      <c r="E404" t="n">
+        <v>32.788</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="n">
+        <v>404</v>
+      </c>
+      <c r="B405" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C405" t="n">
+        <v>0.02384</v>
+      </c>
+      <c r="D405" t="n">
+        <v>0.02384</v>
+      </c>
+      <c r="E405" t="n">
+        <v>32.766</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="n">
+        <v>405</v>
+      </c>
+      <c r="B406" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C406" t="n">
+        <v>0.02375</v>
+      </c>
+      <c r="D406" t="n">
+        <v>0.02375</v>
+      </c>
+      <c r="E406" t="n">
+        <v>32.777</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="n">
+        <v>406</v>
+      </c>
+      <c r="B407" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C407" t="n">
+        <v>0.02395</v>
+      </c>
+      <c r="D407" t="n">
+        <v>0.02395</v>
+      </c>
+      <c r="E407" s="3" t="n">
+        <v>32.804</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="n">
+        <v>407</v>
+      </c>
+      <c r="B408" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C408" t="n">
+        <v>0.02315</v>
+      </c>
+      <c r="D408" t="n">
+        <v>0.02315</v>
+      </c>
+      <c r="E408" t="n">
+        <v>32.777</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="n">
+        <v>408</v>
+      </c>
+      <c r="B409" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C409" t="n">
+        <v>0.02347</v>
+      </c>
+      <c r="D409" t="n">
+        <v>0.02347</v>
+      </c>
+      <c r="E409" t="n">
+        <v>32.792</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="n">
+        <v>409</v>
+      </c>
+      <c r="B410" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C410" t="n">
+        <v>0.02361</v>
+      </c>
+      <c r="D410" t="n">
+        <v>0.02361</v>
+      </c>
+      <c r="E410" t="n">
+        <v>32.782</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="n">
+        <v>410</v>
+      </c>
+      <c r="B411" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C411" t="n">
+        <v>0.02379</v>
+      </c>
+      <c r="D411" t="n">
+        <v>0.02379</v>
+      </c>
+      <c r="E411" t="n">
+        <v>32.776</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="n">
+        <v>411</v>
+      </c>
+      <c r="B412" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C412" t="n">
+        <v>0.02369</v>
+      </c>
+      <c r="D412" t="n">
+        <v>0.02369</v>
+      </c>
+      <c r="E412" t="n">
+        <v>32.776</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="n">
+        <v>412</v>
+      </c>
+      <c r="B413" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C413" t="n">
+        <v>0.02379</v>
+      </c>
+      <c r="D413" t="n">
+        <v>0.02379</v>
+      </c>
+      <c r="E413" t="n">
+        <v>32.779</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="n">
+        <v>413</v>
+      </c>
+      <c r="B414" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C414" t="n">
+        <v>0.02374</v>
+      </c>
+      <c r="D414" t="n">
+        <v>0.02374</v>
+      </c>
+      <c r="E414" t="n">
+        <v>32.794</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="n">
+        <v>414</v>
+      </c>
+      <c r="B415" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C415" t="n">
+        <v>0.02351</v>
+      </c>
+      <c r="D415" t="n">
+        <v>0.02351</v>
+      </c>
+      <c r="E415" t="n">
+        <v>32.787</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="n">
+        <v>415</v>
+      </c>
+      <c r="B416" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C416" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="D416" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="E416" t="n">
+        <v>32.799</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="n">
+        <v>416</v>
+      </c>
+      <c r="B417" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C417" t="n">
+        <v>0.0235</v>
+      </c>
+      <c r="D417" t="n">
+        <v>0.0235</v>
+      </c>
+      <c r="E417" t="n">
+        <v>32.79</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="n">
+        <v>417</v>
+      </c>
+      <c r="B418" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C418" t="n">
+        <v>0.02372</v>
+      </c>
+      <c r="D418" t="n">
+        <v>0.02372</v>
+      </c>
+      <c r="E418" t="n">
+        <v>32.776</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="n">
+        <v>418</v>
+      </c>
+      <c r="B419" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C419" t="n">
+        <v>0.02364</v>
+      </c>
+      <c r="D419" t="n">
+        <v>0.02364</v>
+      </c>
+      <c r="E419" t="n">
+        <v>32.781</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="n">
+        <v>419</v>
+      </c>
+      <c r="B420" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C420" t="n">
+        <v>0.02413</v>
+      </c>
+      <c r="D420" t="n">
+        <v>0.02413</v>
+      </c>
+      <c r="E420" t="n">
+        <v>32.789</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="n">
+        <v>420</v>
+      </c>
+      <c r="B421" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C421" t="n">
+        <v>0.0237</v>
+      </c>
+      <c r="D421" t="n">
+        <v>0.0237</v>
+      </c>
+      <c r="E421" t="n">
+        <v>32.796</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="n">
+        <v>421</v>
+      </c>
+      <c r="B422" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C422" t="n">
+        <v>0.02367</v>
+      </c>
+      <c r="D422" t="n">
+        <v>0.02367</v>
+      </c>
+      <c r="E422" t="n">
+        <v>32.788</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="n">
+        <v>422</v>
+      </c>
+      <c r="B423" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C423" t="n">
+        <v>0.02354</v>
+      </c>
+      <c r="D423" t="n">
+        <v>0.02354</v>
+      </c>
+      <c r="E423" t="n">
+        <v>32.777</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="n">
+        <v>423</v>
+      </c>
+      <c r="B424" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C424" t="n">
+        <v>0.02397</v>
+      </c>
+      <c r="D424" t="n">
+        <v>0.02397</v>
+      </c>
+      <c r="E424" t="n">
+        <v>32.79</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="n">
+        <v>424</v>
+      </c>
+      <c r="B425" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C425" t="n">
+        <v>0.02405</v>
+      </c>
+      <c r="D425" t="n">
+        <v>0.02405</v>
+      </c>
+      <c r="E425" t="n">
+        <v>32.774</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="n">
+        <v>425</v>
+      </c>
+      <c r="B426" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C426" t="n">
+        <v>0.02356</v>
+      </c>
+      <c r="D426" t="n">
+        <v>0.02356</v>
+      </c>
+      <c r="E426" t="n">
+        <v>32.787</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="n">
+        <v>426</v>
+      </c>
+      <c r="B427" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C427" t="n">
+        <v>0.02377</v>
+      </c>
+      <c r="D427" t="n">
+        <v>0.02377</v>
+      </c>
+      <c r="E427" t="n">
+        <v>32.788</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="n">
+        <v>427</v>
+      </c>
+      <c r="B428" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C428" t="n">
+        <v>0.02354</v>
+      </c>
+      <c r="D428" t="n">
+        <v>0.02354</v>
+      </c>
+      <c r="E428" t="n">
+        <v>32.785</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="n">
+        <v>428</v>
+      </c>
+      <c r="B429" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C429" t="n">
+        <v>0.02373</v>
+      </c>
+      <c r="D429" t="n">
+        <v>0.02373</v>
+      </c>
+      <c r="E429" t="n">
+        <v>32.78</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="n">
+        <v>429</v>
+      </c>
+      <c r="B430" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C430" t="n">
+        <v>0.02438</v>
+      </c>
+      <c r="D430" t="n">
+        <v>0.02438</v>
+      </c>
+      <c r="E430" t="n">
+        <v>32.791</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="n">
+        <v>430</v>
+      </c>
+      <c r="B431" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C431" t="n">
+        <v>0.02374</v>
+      </c>
+      <c r="D431" t="n">
+        <v>0.02374</v>
+      </c>
+      <c r="E431" t="n">
+        <v>32.778</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="n">
+        <v>431</v>
+      </c>
+      <c r="B432" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C432" t="n">
+        <v>0.02368</v>
+      </c>
+      <c r="D432" t="n">
+        <v>0.02368</v>
+      </c>
+      <c r="E432" t="n">
+        <v>32.793</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="n">
+        <v>432</v>
+      </c>
+      <c r="B433" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C433" t="n">
+        <v>0.0234</v>
+      </c>
+      <c r="D433" t="n">
+        <v>0.0234</v>
+      </c>
+      <c r="E433" t="n">
+        <v>32.795</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="n">
+        <v>433</v>
+      </c>
+      <c r="B434" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C434" t="n">
+        <v>0.02366</v>
+      </c>
+      <c r="D434" t="n">
+        <v>0.02366</v>
+      </c>
+      <c r="E434" t="n">
+        <v>32.764</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="n">
+        <v>434</v>
+      </c>
+      <c r="B435" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C435" t="n">
+        <v>0.02405</v>
+      </c>
+      <c r="D435" t="n">
+        <v>0.02405</v>
+      </c>
+      <c r="E435" t="n">
+        <v>32.789</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="n">
+        <v>435</v>
+      </c>
+      <c r="B436" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C436" t="n">
+        <v>0.02405</v>
+      </c>
+      <c r="D436" t="n">
+        <v>0.02405</v>
+      </c>
+      <c r="E436" t="n">
+        <v>32.789</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="n">
+        <v>436</v>
+      </c>
+      <c r="B437" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C437" t="n">
+        <v>0.02405</v>
+      </c>
+      <c r="D437" t="n">
+        <v>0.02405</v>
+      </c>
+      <c r="E437" t="n">
+        <v>32.797</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="n">
+        <v>437</v>
+      </c>
+      <c r="B438" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C438" t="n">
+        <v>0.02406</v>
+      </c>
+      <c r="D438" t="n">
+        <v>0.02406</v>
+      </c>
+      <c r="E438" t="n">
+        <v>32.791</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="n">
+        <v>438</v>
+      </c>
+      <c r="B439" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C439" t="n">
+        <v>0.02387</v>
+      </c>
+      <c r="D439" t="n">
+        <v>0.02387</v>
+      </c>
+      <c r="E439" t="n">
+        <v>32.797</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="n">
+        <v>439</v>
+      </c>
+      <c r="B440" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C440" t="n">
+        <v>0.02399</v>
+      </c>
+      <c r="D440" t="n">
+        <v>0.02399</v>
+      </c>
+      <c r="E440" t="n">
+        <v>32.744</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="n">
+        <v>440</v>
+      </c>
+      <c r="B441" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C441" t="n">
+        <v>0.02346</v>
+      </c>
+      <c r="D441" t="n">
+        <v>0.02346</v>
+      </c>
+      <c r="E441" t="n">
+        <v>32.793</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="n">
+        <v>441</v>
+      </c>
+      <c r="B442" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C442" t="n">
+        <v>0.02405</v>
+      </c>
+      <c r="D442" t="n">
+        <v>0.02405</v>
+      </c>
+      <c r="E442" t="n">
+        <v>32.784</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="n">
+        <v>442</v>
+      </c>
+      <c r="B443" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C443" t="n">
+        <v>0.02334</v>
+      </c>
+      <c r="D443" t="n">
+        <v>0.02334</v>
+      </c>
+      <c r="E443" t="n">
+        <v>32.782</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="n">
+        <v>443</v>
+      </c>
+      <c r="B444" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C444" t="n">
+        <v>0.02383</v>
+      </c>
+      <c r="D444" t="n">
+        <v>0.02383</v>
+      </c>
+      <c r="E444" t="n">
+        <v>32.773</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="n">
+        <v>444</v>
+      </c>
+      <c r="B445" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C445" t="n">
+        <v>0.0237</v>
+      </c>
+      <c r="D445" t="n">
+        <v>0.0237</v>
+      </c>
+      <c r="E445" t="n">
+        <v>32.787</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="n">
+        <v>445</v>
+      </c>
+      <c r="B446" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C446" t="n">
+        <v>0.02399</v>
+      </c>
+      <c r="D446" t="n">
+        <v>0.02399</v>
+      </c>
+      <c r="E446" t="n">
+        <v>32.788</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="n">
+        <v>446</v>
+      </c>
+      <c r="B447" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C447" t="n">
+        <v>0.02376</v>
+      </c>
+      <c r="D447" t="n">
+        <v>0.02376</v>
+      </c>
+      <c r="E447" t="n">
+        <v>32.785</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="n">
+        <v>447</v>
+      </c>
+      <c r="B448" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C448" t="n">
+        <v>0.02346</v>
+      </c>
+      <c r="D448" t="n">
+        <v>0.02346</v>
+      </c>
+      <c r="E448" t="n">
+        <v>32.793</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="n">
+        <v>448</v>
+      </c>
+      <c r="B449" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C449" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="D449" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="E449" t="n">
+        <v>32.794</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="n">
+        <v>449</v>
+      </c>
+      <c r="B450" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C450" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="D450" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="E450" t="n">
+        <v>32.785</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="n">
+        <v>450</v>
+      </c>
+      <c r="B451" t="n">
+        <v>6.25e-06</v>
+      </c>
+      <c r="C451" t="n">
+        <v>0.02403</v>
+      </c>
+      <c r="D451" t="n">
+        <v>0.02403</v>
+      </c>
+      <c r="E451" t="n">
+        <v>32.792</v>
       </c>
     </row>
   </sheetData>
